--- a/usuarios_whatsapp_supabase.xlsx
+++ b/usuarios_whatsapp_supabase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Albin Rodríguez\Videos\Nueva carpeta\tejada-pos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B67C2C89-A33F-4F69-BB10-A9C4AD787C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C76202F4-82BF-4A34-9538-723AE86EA587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Todos los Registros'!$A$1:$J$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Usuarios con WhatsApp'!$A$1:$E$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="657">
   <si>
     <t>N°</t>
   </si>
@@ -51,9 +52,6 @@
     <t>Email</t>
   </si>
   <si>
-    <t>Teléfono / WhatsApp</t>
-  </si>
-  <si>
     <t>WhatsApp Normalizado</t>
   </si>
   <si>
@@ -75,9 +73,6 @@
     <t>isaacdelacruz077@gmail.com</t>
   </si>
   <si>
-    <t>849-577-9588 / 809-667-9588</t>
-  </si>
-  <si>
     <t>+18495779588</t>
   </si>
   <si>
@@ -93,15 +88,9 @@
     <t>REYDI TECH SRL</t>
   </si>
   <si>
-    <t>realberto</t>
-  </si>
-  <si>
     <t>realberto@reyditech.com</t>
   </si>
   <si>
-    <t>(829) 639-4882</t>
-  </si>
-  <si>
     <t>+18296394882</t>
   </si>
   <si>
@@ -120,9 +109,6 @@
     <t>christopherrafi@gmail.com</t>
   </si>
   <si>
-    <t>809-812-5981</t>
-  </si>
-  <si>
     <t>+18098125981</t>
   </si>
   <si>
@@ -141,9 +127,6 @@
     <t>rossbell0431@gmail.com</t>
   </si>
   <si>
-    <t>809-517-4225</t>
-  </si>
-  <si>
     <t>+18095174225</t>
   </si>
   <si>
@@ -162,9 +145,6 @@
     <t>gallofarma031@gmail.com</t>
   </si>
   <si>
-    <t>(862)380-0080</t>
-  </si>
-  <si>
     <t>+8623800080</t>
   </si>
   <si>
@@ -183,9 +163,6 @@
     <t>cesaritoelflaco@gmail.com</t>
   </si>
   <si>
-    <t>12500022038</t>
-  </si>
-  <si>
     <t>+12500022038</t>
   </si>
   <si>
@@ -204,9 +181,6 @@
     <t>michellerodriguezv472@gmail.com</t>
   </si>
   <si>
-    <t>8297987521</t>
-  </si>
-  <si>
     <t>+18297987521</t>
   </si>
   <si>
@@ -225,9 +199,6 @@
     <t>estevezedilis88@gmail.com</t>
   </si>
   <si>
-    <t>8095165764</t>
-  </si>
-  <si>
     <t>+18095165764</t>
   </si>
   <si>
@@ -246,9 +217,6 @@
     <t>grullon2011ye@icloud.com</t>
   </si>
   <si>
-    <t>+1 (809) 903‑3173</t>
-  </si>
-  <si>
     <t>+18099033173</t>
   </si>
   <si>
@@ -264,15 +232,9 @@
     <t>Claraluz Gonzalezzapata</t>
   </si>
   <si>
-    <t>Wilsonzapata</t>
-  </si>
-  <si>
     <t>claraluzgonzalezzapata24@gmail.com</t>
   </si>
   <si>
-    <t>8296031078</t>
-  </si>
-  <si>
     <t>+18296031078</t>
   </si>
   <si>
@@ -306,15 +268,9 @@
     <t>Mora multi servicio</t>
   </si>
   <si>
-    <t>moramultiservicio</t>
-  </si>
-  <si>
     <t>e69807257@gmail.com</t>
   </si>
   <si>
-    <t>8493607339</t>
-  </si>
-  <si>
     <t>+18493607339</t>
   </si>
   <si>
@@ -333,9 +289,6 @@
     <t>albertoelenamathieu46@gmail.com</t>
   </si>
   <si>
-    <t>8295611194</t>
-  </si>
-  <si>
     <t>+18295611194</t>
   </si>
   <si>
@@ -354,9 +307,6 @@
     <t>valdezcanario8@gmail.com</t>
   </si>
   <si>
-    <t>8494453441</t>
-  </si>
-  <si>
     <t>+18494453441</t>
   </si>
   <si>
@@ -375,9 +325,6 @@
     <t>zapfixrd@gmail.com</t>
   </si>
   <si>
-    <t>8295426679</t>
-  </si>
-  <si>
     <t>+18295426679</t>
   </si>
   <si>
@@ -396,9 +343,6 @@
     <t>djeysennplk@gmail.com</t>
   </si>
   <si>
-    <t>8295597283</t>
-  </si>
-  <si>
     <t>+18295597283</t>
   </si>
   <si>
@@ -417,9 +361,6 @@
     <t>multiservicioshiglobal@gmail.com</t>
   </si>
   <si>
-    <t>8098496559</t>
-  </si>
-  <si>
     <t>+18098496559</t>
   </si>
   <si>
@@ -438,9 +379,6 @@
     <t>esteisyencarnacion0@gmail.com</t>
   </si>
   <si>
-    <t>829 843 8800</t>
-  </si>
-  <si>
     <t>+18298438800</t>
   </si>
   <si>
@@ -459,9 +397,6 @@
     <t>secundinovargas05@gmail.com</t>
   </si>
   <si>
-    <t>18094886348</t>
-  </si>
-  <si>
     <t>+18094886348</t>
   </si>
   <si>
@@ -480,9 +415,6 @@
     <t>kimberliyperez56@gmail.com</t>
   </si>
   <si>
-    <t>18294749711</t>
-  </si>
-  <si>
     <t>+18294749711</t>
   </si>
   <si>
@@ -501,9 +433,6 @@
     <t>friasesmirna122@gmail.com</t>
   </si>
   <si>
-    <t>8495221894</t>
-  </si>
-  <si>
     <t>+18495221894</t>
   </si>
   <si>
@@ -540,15 +469,9 @@
     <t>Productos Francelis</t>
   </si>
   <si>
-    <t>FRANCELIS</t>
-  </si>
-  <si>
     <t>productosfrancelis@gmail.com</t>
   </si>
   <si>
-    <t>8093573500</t>
-  </si>
-  <si>
     <t>+18093573500</t>
   </si>
   <si>
@@ -585,9 +508,6 @@
     <t>mlantigua189@gmail.com</t>
   </si>
   <si>
-    <t>8094612614</t>
-  </si>
-  <si>
     <t>+18094612614</t>
   </si>
   <si>
@@ -606,9 +526,6 @@
     <t>eliartedecoracionesrd@gmail.com</t>
   </si>
   <si>
-    <t>(809) 652-9182</t>
-  </si>
-  <si>
     <t>+18096529182</t>
   </si>
   <si>
@@ -627,9 +544,6 @@
     <t>mosqueaavalodaysiy@gmail.com</t>
   </si>
   <si>
-    <t>8495414151</t>
-  </si>
-  <si>
     <t>+18495414151</t>
   </si>
   <si>
@@ -648,9 +562,6 @@
     <t>platanosperaltaparron@gmail.com</t>
   </si>
   <si>
-    <t>8298572961</t>
-  </si>
-  <si>
     <t>+18298572961</t>
   </si>
   <si>
@@ -669,9 +580,6 @@
     <t>osdaibagon98@gmail.com</t>
   </si>
   <si>
-    <t>3505453939</t>
-  </si>
-  <si>
     <t>+573505453939</t>
   </si>
   <si>
@@ -690,9 +598,6 @@
     <t>kati22mt@gmail.com</t>
   </si>
   <si>
-    <t>whatsApp +18495951202</t>
-  </si>
-  <si>
     <t>+18495951202</t>
   </si>
   <si>
@@ -711,9 +616,6 @@
     <t>ing.yildatoribio@gmail.com</t>
   </si>
   <si>
-    <t>8096543301</t>
-  </si>
-  <si>
     <t>+18096543301</t>
   </si>
   <si>
@@ -729,15 +631,9 @@
     <t>YOMI</t>
   </si>
   <si>
-    <t>Yomairis30</t>
-  </si>
-  <si>
     <t>yomarodriguez40@gmail.com</t>
   </si>
   <si>
-    <t>8494045619</t>
-  </si>
-  <si>
     <t>+18494045619</t>
   </si>
   <si>
@@ -756,9 +652,6 @@
     <t>keylamartinez1812@gmail.com</t>
   </si>
   <si>
-    <t>8098193766</t>
-  </si>
-  <si>
     <t>+18098193766</t>
   </si>
   <si>
@@ -777,9 +670,6 @@
     <t>merym7053@gmail.com</t>
   </si>
   <si>
-    <t>8099577269</t>
-  </si>
-  <si>
     <t>+18099577269</t>
   </si>
   <si>
@@ -798,9 +688,6 @@
     <t>marrerosolar@gmail.com</t>
   </si>
   <si>
-    <t>53566034</t>
-  </si>
-  <si>
     <t>+5353566034</t>
   </si>
   <si>
@@ -816,15 +703,9 @@
     <t>Carlos Baltazar</t>
   </si>
   <si>
-    <t>Cbz007</t>
-  </si>
-  <si>
     <t>huevosx81@gmail.com</t>
   </si>
   <si>
-    <t>5511414227</t>
-  </si>
-  <si>
     <t>+525511414227</t>
   </si>
   <si>
@@ -843,9 +724,6 @@
     <t>darvybetance@gmail.com</t>
   </si>
   <si>
-    <t>8098098099</t>
-  </si>
-  <si>
     <t>+18098098099</t>
   </si>
   <si>
@@ -864,9 +742,6 @@
     <t>atellez780724@gmail.com</t>
   </si>
   <si>
-    <t>5352164763</t>
-  </si>
-  <si>
     <t>+5352164763</t>
   </si>
   <si>
@@ -885,9 +760,6 @@
     <t>lacteososcar498@gmail.com</t>
   </si>
   <si>
-    <t>573505453939</t>
-  </si>
-  <si>
     <t>05/06/2026 19:56</t>
   </si>
   <si>
@@ -900,9 +772,6 @@
     <t>jhonnyarismendy1398@gmail.com</t>
   </si>
   <si>
-    <t>8094620486</t>
-  </si>
-  <si>
     <t>+18094620486</t>
   </si>
   <si>
@@ -921,9 +790,6 @@
     <t>kyrvapestore@gmail.com</t>
   </si>
   <si>
-    <t>8299309774</t>
-  </si>
-  <si>
     <t>+18299309774</t>
   </si>
   <si>
@@ -939,15 +805,9 @@
     <t>María Elena Rosario</t>
   </si>
   <si>
-    <t>Maria</t>
-  </si>
-  <si>
     <t>mariaelenarosario574@gmail.com</t>
   </si>
   <si>
-    <t>+1 (809) 358-1046</t>
-  </si>
-  <si>
     <t>+18093581046</t>
   </si>
   <si>
@@ -966,9 +826,6 @@
     <t>vocetin5s@gmail.com</t>
   </si>
   <si>
-    <t>8493404986</t>
-  </si>
-  <si>
     <t>+18493404986</t>
   </si>
   <si>
@@ -987,9 +844,6 @@
     <t>encarnacionv30@gmail.com</t>
   </si>
   <si>
-    <t>8093710966</t>
-  </si>
-  <si>
     <t>+18093710966</t>
   </si>
   <si>
@@ -1008,9 +862,6 @@
     <t>lucarly6@gmail.com</t>
   </si>
   <si>
-    <t>8084221591</t>
-  </si>
-  <si>
     <t>+8084221591</t>
   </si>
   <si>
@@ -1029,9 +880,6 @@
     <t>donderobert73@gmail.com</t>
   </si>
   <si>
-    <t>+58 412 5076850</t>
-  </si>
-  <si>
     <t>+584125076850</t>
   </si>
   <si>
@@ -1050,9 +898,6 @@
     <t>novasjeannys279@gmail.com</t>
   </si>
   <si>
-    <t>809 000 2209</t>
-  </si>
-  <si>
     <t>+18090002209</t>
   </si>
   <si>
@@ -1086,9 +931,6 @@
     <t>Recargas GALES JT</t>
   </si>
   <si>
-    <t>JhonJT05</t>
-  </si>
-  <si>
     <t>jhontapuy05@gmail.com</t>
   </si>
   <si>
@@ -1146,9 +988,6 @@
     <t>maikerramires9@gmail.com</t>
   </si>
   <si>
-    <t>4126938758</t>
-  </si>
-  <si>
     <t>+584126938758</t>
   </si>
   <si>
@@ -1167,9 +1006,6 @@
     <t>helenalcantara77@gmail.com</t>
   </si>
   <si>
-    <t>8098447670</t>
-  </si>
-  <si>
     <t>+18098447670</t>
   </si>
   <si>
@@ -1206,9 +1042,6 @@
     <t>carolsulbaran2@gmail.com</t>
   </si>
   <si>
-    <t>58 412804028</t>
-  </si>
-  <si>
     <t>+58412804028</t>
   </si>
   <si>
@@ -1224,9 +1057,6 @@
     <t>Sublimación Reyes</t>
   </si>
   <si>
-    <t>Reyes</t>
-  </si>
-  <si>
     <t>rcastillomaycol1612@gmail.com</t>
   </si>
   <si>
@@ -1248,9 +1078,6 @@
     <t>fleandra511@gmail.com</t>
   </si>
   <si>
-    <t>8092518684</t>
-  </si>
-  <si>
     <t>+18092518684</t>
   </si>
   <si>
@@ -1269,9 +1096,6 @@
     <t>yrg.850917@gmail.com</t>
   </si>
   <si>
-    <t>53462653</t>
-  </si>
-  <si>
     <t>+5353462653</t>
   </si>
   <si>
@@ -1290,9 +1114,6 @@
     <t>cardenacristofer4@gmail.com</t>
   </si>
   <si>
-    <t>8493759636</t>
-  </si>
-  <si>
     <t>+18493759636</t>
   </si>
   <si>
@@ -1311,9 +1132,6 @@
     <t>felizsalazarkarolay@gmail.com</t>
   </si>
   <si>
-    <t>8094565213</t>
-  </si>
-  <si>
     <t>+18094565213</t>
   </si>
   <si>
@@ -1332,9 +1150,6 @@
     <t>kendrihenriquezb@gmail.com</t>
   </si>
   <si>
-    <t>8492536728</t>
-  </si>
-  <si>
     <t>+18492536728</t>
   </si>
   <si>
@@ -1350,15 +1165,9 @@
     <t>julio yordanis florez peres</t>
   </si>
   <si>
-    <t>YORDANIS</t>
-  </si>
-  <si>
     <t>julioyordanis@gmail.com</t>
   </si>
   <si>
-    <t>8298425957</t>
-  </si>
-  <si>
     <t>+18298425957</t>
   </si>
   <si>
@@ -1377,9 +1186,6 @@
     <t>miguellinares1323@gmail.com</t>
   </si>
   <si>
-    <t>8296581941</t>
-  </si>
-  <si>
     <t>+18296581941</t>
   </si>
   <si>
@@ -1422,9 +1228,6 @@
     <t>steven.paul.diaz@gmail.com</t>
   </si>
   <si>
-    <t>8097383838</t>
-  </si>
-  <si>
     <t>+18097383838</t>
   </si>
   <si>
@@ -1473,15 +1276,9 @@
     <t>Imverter Venta y Servicio</t>
   </si>
   <si>
-    <t>Gioribel</t>
-  </si>
-  <si>
     <t>daniel.ovj25@gmail.com</t>
   </si>
   <si>
-    <t>18098970988</t>
-  </si>
-  <si>
     <t>+18098970988</t>
   </si>
   <si>
@@ -1500,9 +1297,6 @@
     <t>servicioinvasa@outlook.com</t>
   </si>
   <si>
-    <t>8095392143</t>
-  </si>
-  <si>
     <t>+18095392143</t>
   </si>
   <si>
@@ -1518,15 +1312,9 @@
     <t>nasar woovensqui</t>
   </si>
   <si>
-    <t>nasar</t>
-  </si>
-  <si>
     <t>nasarwoovensqui@gmail.com</t>
   </si>
   <si>
-    <t>+1 829 630-61 26</t>
-  </si>
-  <si>
     <t>+18296306126</t>
   </si>
   <si>
@@ -1545,9 +1333,6 @@
     <t>nanan13331832@gmail.com</t>
   </si>
   <si>
-    <t>6866067206</t>
-  </si>
-  <si>
     <t>+526866067206</t>
   </si>
   <si>
@@ -1566,9 +1351,6 @@
     <t>av6897088@gmail.com</t>
   </si>
   <si>
-    <t>8292976712</t>
-  </si>
-  <si>
     <t>+18292976712</t>
   </si>
   <si>
@@ -1587,9 +1369,6 @@
     <t>crisellinalmonte33@gmail.com</t>
   </si>
   <si>
-    <t>3476589919</t>
-  </si>
-  <si>
     <t>+573476589919</t>
   </si>
   <si>
@@ -1608,9 +1387,6 @@
     <t>grupoohla@gmail.com</t>
   </si>
   <si>
-    <t>8393783388</t>
-  </si>
-  <si>
     <t>+18393783388</t>
   </si>
   <si>
@@ -1626,15 +1402,9 @@
     <t>ZIHOR Tienda de Uniformes</t>
   </si>
   <si>
-    <t xml:space="preserve">JENNIFER CEDANO </t>
-  </si>
-  <si>
     <t>jennifercedanosanchez@gmail.com</t>
   </si>
   <si>
-    <t>829-968-1146</t>
-  </si>
-  <si>
     <t>+18299681146</t>
   </si>
   <si>
@@ -1669,9 +1439,6 @@
   </si>
   <si>
     <t>winibelpaulino25@gmail.com</t>
-  </si>
-  <si>
-    <t>8094997511</t>
   </si>
   <si>
     <t>+18094997511</t>
@@ -2271,7 +2038,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2279,13 +2046,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2645,2217 +2428,1758 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I88"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="35.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="35.83203125" customWidth="1"/>
-    <col min="5" max="5" width="25.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="35.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
+    <col min="2" max="3" width="35.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="7" max="7" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
       </c>
       <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s">
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>18</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
+      <c r="B15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" t="s">
+        <v>90</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>22</v>
       </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="B16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" t="s">
+        <v>96</v>
+      </c>
+      <c r="G16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>26</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
+      <c r="B20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
+      <c r="B21" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F21" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="B22" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>32</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="B24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" t="s">
+        <v>151</v>
+      </c>
+      <c r="G24" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>33</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B25" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F25" t="s">
+        <v>157</v>
+      </c>
+      <c r="G25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
+      <c r="B26" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F26" t="s">
+        <v>163</v>
+      </c>
+      <c r="G26" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>35</v>
       </c>
-      <c r="G5" t="s">
+      <c r="B27" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27" t="s">
+        <v>169</v>
+      </c>
+      <c r="G27" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>36</v>
       </c>
-      <c r="H5" t="s">
+      <c r="B28" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F28" t="s">
+        <v>175</v>
+      </c>
+      <c r="G28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>37</v>
       </c>
-      <c r="I5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B29" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" t="s">
+        <v>181</v>
+      </c>
+      <c r="G29" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>39</v>
       </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B30" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F30" t="s">
+        <v>187</v>
+      </c>
+      <c r="G30" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>41</v>
       </c>
-      <c r="F6" t="s">
+      <c r="B31" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F31" t="s">
+        <v>193</v>
+      </c>
+      <c r="G31" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>42</v>
       </c>
-      <c r="G6" t="s">
+      <c r="B32" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F32" t="s">
+        <v>199</v>
+      </c>
+      <c r="G32" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>43</v>
       </c>
-      <c r="H6" t="s">
+      <c r="B33" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F33" t="s">
+        <v>205</v>
+      </c>
+      <c r="G33" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>44</v>
       </c>
-      <c r="I6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="B34" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F34" t="s">
+        <v>211</v>
+      </c>
+      <c r="G34" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>46</v>
       </c>
-      <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="B35" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F35" t="s">
+        <v>217</v>
+      </c>
+      <c r="G35" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>47</v>
       </c>
-      <c r="E7" t="s">
+      <c r="B36" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F36" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
         <v>48</v>
       </c>
-      <c r="F7" t="s">
+      <c r="B37" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F37" t="s">
+        <v>229</v>
+      </c>
+      <c r="G37" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>49</v>
       </c>
-      <c r="G7" t="s">
+      <c r="B38" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F38" t="s">
+        <v>235</v>
+      </c>
+      <c r="G38" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
         <v>50</v>
       </c>
-      <c r="H7" t="s">
+      <c r="B39" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F39" t="s">
+        <v>181</v>
+      </c>
+      <c r="G39" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>51</v>
       </c>
-      <c r="I7" t="s">
+      <c r="B40" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F40" t="s">
+        <v>245</v>
+      </c>
+      <c r="G40" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B41" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F41" t="s">
+        <v>251</v>
+      </c>
+      <c r="G41" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>53</v>
       </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B42" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F42" t="s">
+        <v>257</v>
+      </c>
+      <c r="G42" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
         <v>54</v>
       </c>
-      <c r="E8" t="s">
+      <c r="B43" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F43" t="s">
+        <v>263</v>
+      </c>
+      <c r="G43" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
         <v>55</v>
       </c>
-      <c r="F8" t="s">
+      <c r="B44" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F44" t="s">
+        <v>269</v>
+      </c>
+      <c r="G44" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
         <v>56</v>
       </c>
-      <c r="G8" t="s">
+      <c r="B45" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F45" t="s">
+        <v>275</v>
+      </c>
+      <c r="G45" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>57</v>
       </c>
-      <c r="H8" t="s">
+      <c r="B46" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F46" t="s">
+        <v>281</v>
+      </c>
+      <c r="G46" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
         <v>58</v>
       </c>
-      <c r="I8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B47" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F47" t="s">
+        <v>287</v>
+      </c>
+      <c r="G47" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
         <v>60</v>
       </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="B48" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F48" t="s">
+        <v>293</v>
+      </c>
+      <c r="G48" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
         <v>62</v>
       </c>
-      <c r="F9" t="s">
+      <c r="B49" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F49" t="s">
+        <v>299</v>
+      </c>
+      <c r="G49" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
         <v>63</v>
       </c>
-      <c r="G9" t="s">
+      <c r="B50" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F50" t="s">
+        <v>305</v>
+      </c>
+      <c r="G50" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="2">
         <v>64</v>
       </c>
-      <c r="H9" t="s">
+      <c r="B51" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F51" t="s">
+        <v>311</v>
+      </c>
+      <c r="G51" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
         <v>65</v>
       </c>
-      <c r="I9" t="s">
+      <c r="B52" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F52" t="s">
+        <v>317</v>
+      </c>
+      <c r="G52" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
         <v>66</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B53" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F53" t="s">
+        <v>323</v>
+      </c>
+      <c r="G53" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
         <v>67</v>
       </c>
-      <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="B54" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F54" t="s">
+        <v>329</v>
+      </c>
+      <c r="G54" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
         <v>68</v>
       </c>
-      <c r="E10" t="s">
+      <c r="B55" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F55" t="s">
+        <v>335</v>
+      </c>
+      <c r="G55" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
         <v>69</v>
       </c>
-      <c r="F10" t="s">
+      <c r="B56" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F56" t="s">
+        <v>341</v>
+      </c>
+      <c r="G56" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
         <v>70</v>
       </c>
-      <c r="G10" t="s">
+      <c r="B57" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F57" t="s">
+        <v>347</v>
+      </c>
+      <c r="G57" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
         <v>71</v>
       </c>
-      <c r="H10" t="s">
+      <c r="B58" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F58" t="s">
+        <v>353</v>
+      </c>
+      <c r="G58" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="2">
         <v>72</v>
       </c>
-      <c r="I10" t="s">
+      <c r="B59" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F59" t="s">
+        <v>359</v>
+      </c>
+      <c r="G59" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
         <v>73</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B60" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F60" t="s">
+        <v>365</v>
+      </c>
+      <c r="G60" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
         <v>74</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B61" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F61" t="s">
+        <v>371</v>
+      </c>
+      <c r="G61" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
         <v>75</v>
       </c>
-      <c r="D11" t="s">
+      <c r="B62" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F62" t="s">
+        <v>377</v>
+      </c>
+      <c r="G62" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
         <v>76</v>
       </c>
-      <c r="E11" t="s">
-        <v>77</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="B63" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="F63" t="s">
+        <v>383</v>
+      </c>
+      <c r="G63" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
         <v>78</v>
       </c>
-      <c r="G11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="B64" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F64" t="s">
+        <v>397</v>
+      </c>
+      <c r="G64" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
         <v>80</v>
       </c>
-      <c r="I11" t="s">
+      <c r="B65" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F65" t="s">
+        <v>263</v>
+      </c>
+      <c r="G65" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
         <v>81</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="B66" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F66" t="s">
+        <v>414</v>
+      </c>
+      <c r="G66" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
         <v>82</v>
       </c>
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="B67" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F67" t="s">
+        <v>420</v>
+      </c>
+      <c r="G67" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="2">
         <v>83</v>
       </c>
-      <c r="E12" t="s">
+      <c r="B68" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F68" t="s">
+        <v>426</v>
+      </c>
+      <c r="G68" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" s="2">
         <v>84</v>
       </c>
-      <c r="F12" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="B69" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="F69" t="s">
+        <v>432</v>
+      </c>
+      <c r="G69" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
         <v>85</v>
       </c>
-      <c r="H12" t="s">
+      <c r="B70" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F70" t="s">
+        <v>438</v>
+      </c>
+      <c r="G70" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" s="2">
         <v>86</v>
       </c>
-      <c r="I12" t="s">
+      <c r="B71" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F71" t="s">
+        <v>444</v>
+      </c>
+      <c r="G71" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
         <v>87</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="B72" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="F72" t="s">
+        <v>450</v>
+      </c>
+      <c r="G72" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" s="2">
         <v>88</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B73" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F73" t="s">
+        <v>456</v>
+      </c>
+      <c r="G73" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" s="2">
         <v>89</v>
       </c>
-      <c r="D13" t="s">
+      <c r="B74" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="F74" t="s">
+        <v>462</v>
+      </c>
+      <c r="G74" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" s="2">
         <v>90</v>
       </c>
-      <c r="E13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" t="s">
-        <v>94</v>
-      </c>
-      <c r="I13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" t="s">
-        <v>98</v>
-      </c>
-      <c r="F14" t="s">
-        <v>99</v>
-      </c>
-      <c r="G14" t="s">
-        <v>100</v>
-      </c>
-      <c r="H14" t="s">
-        <v>101</v>
-      </c>
-      <c r="I14" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" t="s">
-        <v>105</v>
-      </c>
-      <c r="F15" t="s">
-        <v>106</v>
-      </c>
-      <c r="G15" t="s">
-        <v>107</v>
-      </c>
-      <c r="H15" t="s">
-        <v>108</v>
-      </c>
-      <c r="I15" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" t="s">
-        <v>112</v>
-      </c>
-      <c r="F16" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" t="s">
-        <v>114</v>
-      </c>
-      <c r="H16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I16" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>24</v>
-      </c>
-      <c r="B17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" t="s">
-        <v>119</v>
-      </c>
-      <c r="F17" t="s">
-        <v>120</v>
-      </c>
-      <c r="G17" t="s">
-        <v>121</v>
-      </c>
-      <c r="H17" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>25</v>
-      </c>
-      <c r="B18" t="s">
-        <v>124</v>
-      </c>
-      <c r="C18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E18" t="s">
-        <v>126</v>
-      </c>
-      <c r="F18" t="s">
-        <v>127</v>
-      </c>
-      <c r="G18" t="s">
-        <v>128</v>
-      </c>
-      <c r="H18" t="s">
-        <v>129</v>
-      </c>
-      <c r="I18" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>26</v>
-      </c>
-      <c r="B19" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D19" t="s">
-        <v>132</v>
-      </c>
-      <c r="E19" t="s">
-        <v>133</v>
-      </c>
-      <c r="F19" t="s">
-        <v>134</v>
-      </c>
-      <c r="G19" t="s">
-        <v>135</v>
-      </c>
-      <c r="H19" t="s">
-        <v>136</v>
-      </c>
-      <c r="I19" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>27</v>
-      </c>
-      <c r="B20" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" t="s">
-        <v>139</v>
-      </c>
-      <c r="E20" t="s">
-        <v>140</v>
-      </c>
-      <c r="F20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G20" t="s">
-        <v>142</v>
-      </c>
-      <c r="H20" t="s">
-        <v>143</v>
-      </c>
-      <c r="I20" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>28</v>
-      </c>
-      <c r="B21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" t="s">
-        <v>146</v>
-      </c>
-      <c r="E21" t="s">
-        <v>147</v>
-      </c>
-      <c r="F21" t="s">
-        <v>148</v>
-      </c>
-      <c r="G21" t="s">
-        <v>149</v>
-      </c>
-      <c r="H21" t="s">
-        <v>150</v>
-      </c>
-      <c r="I21" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>29</v>
-      </c>
-      <c r="B22" t="s">
-        <v>152</v>
-      </c>
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" t="s">
-        <v>154</v>
-      </c>
-      <c r="F22" t="s">
-        <v>155</v>
-      </c>
-      <c r="G22" t="s">
-        <v>156</v>
-      </c>
-      <c r="H22" t="s">
-        <v>157</v>
-      </c>
-      <c r="I22" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>31</v>
-      </c>
-      <c r="B23" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" t="s">
-        <v>167</v>
-      </c>
-      <c r="D23" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" t="s">
-        <v>169</v>
-      </c>
-      <c r="F23" t="s">
-        <v>170</v>
-      </c>
-      <c r="G23" t="s">
-        <v>171</v>
-      </c>
-      <c r="H23" t="s">
-        <v>172</v>
-      </c>
-      <c r="I23" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>32</v>
-      </c>
-      <c r="B24" t="s">
-        <v>174</v>
-      </c>
-      <c r="C24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" t="s">
-        <v>175</v>
-      </c>
-      <c r="E24" t="s">
-        <v>176</v>
-      </c>
-      <c r="F24" t="s">
-        <v>176</v>
-      </c>
-      <c r="G24" t="s">
-        <v>177</v>
-      </c>
-      <c r="H24" t="s">
-        <v>178</v>
-      </c>
-      <c r="I24" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>33</v>
-      </c>
-      <c r="B25" t="s">
-        <v>180</v>
-      </c>
-      <c r="C25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" t="s">
-        <v>181</v>
-      </c>
-      <c r="E25" t="s">
-        <v>182</v>
-      </c>
-      <c r="F25" t="s">
-        <v>183</v>
-      </c>
-      <c r="G25" t="s">
-        <v>184</v>
-      </c>
-      <c r="H25" t="s">
-        <v>185</v>
-      </c>
-      <c r="I25" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>34</v>
-      </c>
-      <c r="B26" t="s">
-        <v>187</v>
-      </c>
-      <c r="C26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" t="s">
-        <v>188</v>
-      </c>
-      <c r="E26" t="s">
-        <v>189</v>
-      </c>
-      <c r="F26" t="s">
-        <v>190</v>
-      </c>
-      <c r="G26" t="s">
-        <v>191</v>
-      </c>
-      <c r="H26" t="s">
-        <v>192</v>
-      </c>
-      <c r="I26" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
-        <v>194</v>
-      </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" t="s">
-        <v>195</v>
-      </c>
-      <c r="E27" t="s">
-        <v>196</v>
-      </c>
-      <c r="F27" t="s">
-        <v>197</v>
-      </c>
-      <c r="G27" t="s">
-        <v>198</v>
-      </c>
-      <c r="H27" t="s">
-        <v>199</v>
-      </c>
-      <c r="I27" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>36</v>
-      </c>
-      <c r="B28" t="s">
-        <v>201</v>
-      </c>
-      <c r="C28" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" t="s">
-        <v>202</v>
-      </c>
-      <c r="E28" t="s">
-        <v>203</v>
-      </c>
-      <c r="F28" t="s">
-        <v>204</v>
-      </c>
-      <c r="G28" t="s">
-        <v>205</v>
-      </c>
-      <c r="H28" t="s">
-        <v>206</v>
-      </c>
-      <c r="I28" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>37</v>
-      </c>
-      <c r="B29" t="s">
-        <v>208</v>
-      </c>
-      <c r="C29" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" t="s">
-        <v>209</v>
-      </c>
-      <c r="E29" t="s">
-        <v>210</v>
-      </c>
-      <c r="F29" t="s">
-        <v>211</v>
-      </c>
-      <c r="G29" t="s">
-        <v>212</v>
-      </c>
-      <c r="H29" t="s">
-        <v>213</v>
-      </c>
-      <c r="I29" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>39</v>
-      </c>
-      <c r="B30" t="s">
-        <v>215</v>
-      </c>
-      <c r="C30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" t="s">
-        <v>216</v>
-      </c>
-      <c r="E30" t="s">
-        <v>217</v>
-      </c>
-      <c r="F30" t="s">
-        <v>218</v>
-      </c>
-      <c r="G30" t="s">
-        <v>219</v>
-      </c>
-      <c r="H30" t="s">
-        <v>220</v>
-      </c>
-      <c r="I30" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>41</v>
-      </c>
-      <c r="B31" t="s">
-        <v>222</v>
-      </c>
-      <c r="C31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" t="s">
-        <v>223</v>
-      </c>
-      <c r="E31" t="s">
-        <v>224</v>
-      </c>
-      <c r="F31" t="s">
-        <v>225</v>
-      </c>
-      <c r="G31" t="s">
-        <v>226</v>
-      </c>
-      <c r="H31" t="s">
-        <v>227</v>
-      </c>
-      <c r="I31" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>42</v>
-      </c>
-      <c r="B32" t="s">
-        <v>229</v>
-      </c>
-      <c r="C32" t="s">
-        <v>230</v>
-      </c>
-      <c r="D32" t="s">
-        <v>231</v>
-      </c>
-      <c r="E32" t="s">
-        <v>232</v>
-      </c>
-      <c r="F32" t="s">
-        <v>233</v>
-      </c>
-      <c r="G32" t="s">
-        <v>234</v>
-      </c>
-      <c r="H32" t="s">
-        <v>235</v>
-      </c>
-      <c r="I32" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>43</v>
-      </c>
-      <c r="B33" t="s">
-        <v>237</v>
-      </c>
-      <c r="C33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" t="s">
-        <v>238</v>
-      </c>
-      <c r="E33" t="s">
-        <v>239</v>
-      </c>
-      <c r="F33" t="s">
-        <v>240</v>
-      </c>
-      <c r="G33" t="s">
-        <v>241</v>
-      </c>
-      <c r="H33" t="s">
-        <v>242</v>
-      </c>
-      <c r="I33" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>44</v>
-      </c>
-      <c r="B34" t="s">
-        <v>244</v>
-      </c>
-      <c r="C34" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" t="s">
-        <v>245</v>
-      </c>
-      <c r="E34" t="s">
-        <v>246</v>
-      </c>
-      <c r="F34" t="s">
-        <v>247</v>
-      </c>
-      <c r="G34" t="s">
-        <v>248</v>
-      </c>
-      <c r="H34" t="s">
-        <v>249</v>
-      </c>
-      <c r="I34" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>46</v>
-      </c>
-      <c r="B35" t="s">
-        <v>251</v>
-      </c>
-      <c r="C35" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" t="s">
-        <v>252</v>
-      </c>
-      <c r="E35" t="s">
-        <v>253</v>
-      </c>
-      <c r="F35" t="s">
-        <v>254</v>
-      </c>
-      <c r="G35" t="s">
-        <v>255</v>
-      </c>
-      <c r="H35" t="s">
-        <v>256</v>
-      </c>
-      <c r="I35" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>47</v>
-      </c>
-      <c r="B36" t="s">
-        <v>258</v>
-      </c>
-      <c r="C36" t="s">
-        <v>259</v>
-      </c>
-      <c r="D36" t="s">
-        <v>260</v>
-      </c>
-      <c r="E36" t="s">
-        <v>261</v>
-      </c>
-      <c r="F36" t="s">
-        <v>262</v>
-      </c>
-      <c r="G36" t="s">
-        <v>263</v>
-      </c>
-      <c r="H36" t="s">
-        <v>264</v>
-      </c>
-      <c r="I36" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>48</v>
-      </c>
-      <c r="B37" t="s">
-        <v>266</v>
-      </c>
-      <c r="C37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" t="s">
-        <v>267</v>
-      </c>
-      <c r="E37" t="s">
-        <v>268</v>
-      </c>
-      <c r="F37" t="s">
-        <v>269</v>
-      </c>
-      <c r="G37" t="s">
-        <v>270</v>
-      </c>
-      <c r="H37" t="s">
-        <v>271</v>
-      </c>
-      <c r="I37" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>49</v>
-      </c>
-      <c r="B38" t="s">
-        <v>273</v>
-      </c>
-      <c r="C38" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" t="s">
-        <v>274</v>
-      </c>
-      <c r="E38" t="s">
-        <v>275</v>
-      </c>
-      <c r="F38" t="s">
-        <v>276</v>
-      </c>
-      <c r="G38" t="s">
-        <v>277</v>
-      </c>
-      <c r="H38" t="s">
-        <v>278</v>
-      </c>
-      <c r="I38" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>50</v>
-      </c>
-      <c r="B39" t="s">
-        <v>280</v>
-      </c>
-      <c r="C39" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" t="s">
-        <v>281</v>
-      </c>
-      <c r="E39" t="s">
-        <v>282</v>
-      </c>
-      <c r="F39" t="s">
-        <v>211</v>
-      </c>
-      <c r="G39" t="s">
-        <v>212</v>
-      </c>
-      <c r="H39" t="s">
-        <v>283</v>
-      </c>
-      <c r="I39" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>51</v>
-      </c>
-      <c r="B40" t="s">
-        <v>285</v>
-      </c>
-      <c r="C40" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" t="s">
-        <v>286</v>
-      </c>
-      <c r="E40" t="s">
-        <v>287</v>
-      </c>
-      <c r="F40" t="s">
-        <v>288</v>
-      </c>
-      <c r="G40" t="s">
-        <v>289</v>
-      </c>
-      <c r="H40" t="s">
-        <v>290</v>
-      </c>
-      <c r="I40" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>52</v>
-      </c>
-      <c r="B41" t="s">
-        <v>292</v>
-      </c>
-      <c r="C41" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" t="s">
-        <v>293</v>
-      </c>
-      <c r="E41" t="s">
-        <v>294</v>
-      </c>
-      <c r="F41" t="s">
-        <v>295</v>
-      </c>
-      <c r="G41" t="s">
-        <v>296</v>
-      </c>
-      <c r="H41" t="s">
-        <v>297</v>
-      </c>
-      <c r="I41" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>53</v>
-      </c>
-      <c r="B42" t="s">
-        <v>299</v>
-      </c>
-      <c r="C42" t="s">
-        <v>300</v>
-      </c>
-      <c r="D42" t="s">
-        <v>301</v>
-      </c>
-      <c r="E42" t="s">
-        <v>302</v>
-      </c>
-      <c r="F42" t="s">
-        <v>303</v>
-      </c>
-      <c r="G42" t="s">
-        <v>304</v>
-      </c>
-      <c r="H42" t="s">
-        <v>305</v>
-      </c>
-      <c r="I42" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>54</v>
-      </c>
-      <c r="B43" t="s">
-        <v>307</v>
-      </c>
-      <c r="C43" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" t="s">
-        <v>308</v>
-      </c>
-      <c r="E43" t="s">
-        <v>309</v>
-      </c>
-      <c r="F43" t="s">
-        <v>310</v>
-      </c>
-      <c r="G43" t="s">
-        <v>311</v>
-      </c>
-      <c r="H43" t="s">
-        <v>312</v>
-      </c>
-      <c r="I43" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>55</v>
-      </c>
-      <c r="B44" t="s">
-        <v>314</v>
-      </c>
-      <c r="C44" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" t="s">
-        <v>315</v>
-      </c>
-      <c r="E44" t="s">
-        <v>316</v>
-      </c>
-      <c r="F44" t="s">
-        <v>317</v>
-      </c>
-      <c r="G44" t="s">
-        <v>318</v>
-      </c>
-      <c r="H44" t="s">
-        <v>319</v>
-      </c>
-      <c r="I44" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>56</v>
-      </c>
-      <c r="B45" t="s">
-        <v>321</v>
-      </c>
-      <c r="C45" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" t="s">
-        <v>322</v>
-      </c>
-      <c r="E45" t="s">
-        <v>323</v>
-      </c>
-      <c r="F45" t="s">
-        <v>324</v>
-      </c>
-      <c r="G45" t="s">
-        <v>325</v>
-      </c>
-      <c r="H45" t="s">
-        <v>326</v>
-      </c>
-      <c r="I45" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>57</v>
-      </c>
-      <c r="B46" t="s">
-        <v>328</v>
-      </c>
-      <c r="C46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" t="s">
-        <v>329</v>
-      </c>
-      <c r="E46" t="s">
-        <v>330</v>
-      </c>
-      <c r="F46" t="s">
-        <v>331</v>
-      </c>
-      <c r="G46" t="s">
-        <v>332</v>
-      </c>
-      <c r="H46" t="s">
-        <v>333</v>
-      </c>
-      <c r="I46" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>58</v>
-      </c>
-      <c r="B47" t="s">
-        <v>335</v>
-      </c>
-      <c r="C47" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" t="s">
-        <v>336</v>
-      </c>
-      <c r="E47" t="s">
-        <v>337</v>
-      </c>
-      <c r="F47" t="s">
-        <v>338</v>
-      </c>
-      <c r="G47" t="s">
-        <v>339</v>
-      </c>
-      <c r="H47" t="s">
-        <v>340</v>
-      </c>
-      <c r="I47" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>60</v>
-      </c>
-      <c r="B48" t="s">
-        <v>342</v>
-      </c>
-      <c r="C48" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" t="s">
-        <v>343</v>
-      </c>
-      <c r="E48" t="s">
-        <v>344</v>
-      </c>
-      <c r="F48" t="s">
-        <v>344</v>
-      </c>
-      <c r="G48" t="s">
-        <v>345</v>
-      </c>
-      <c r="H48" t="s">
-        <v>346</v>
-      </c>
-      <c r="I48" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>62</v>
-      </c>
-      <c r="B49" t="s">
-        <v>348</v>
-      </c>
-      <c r="C49" t="s">
-        <v>349</v>
-      </c>
-      <c r="D49" t="s">
-        <v>350</v>
-      </c>
-      <c r="E49" t="s">
-        <v>351</v>
-      </c>
-      <c r="F49" t="s">
-        <v>351</v>
-      </c>
-      <c r="G49" t="s">
-        <v>352</v>
-      </c>
-      <c r="H49" t="s">
-        <v>353</v>
-      </c>
-      <c r="I49" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>63</v>
-      </c>
-      <c r="B50" t="s">
-        <v>355</v>
-      </c>
-      <c r="C50" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" t="s">
-        <v>356</v>
-      </c>
-      <c r="E50" t="s">
-        <v>357</v>
-      </c>
-      <c r="F50" t="s">
-        <v>357</v>
-      </c>
-      <c r="G50" t="s">
-        <v>358</v>
-      </c>
-      <c r="H50" t="s">
-        <v>359</v>
-      </c>
-      <c r="I50" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>64</v>
-      </c>
-      <c r="B51" t="s">
-        <v>361</v>
-      </c>
-      <c r="C51" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" t="s">
-        <v>362</v>
-      </c>
-      <c r="E51" t="s">
-        <v>363</v>
-      </c>
-      <c r="F51" t="s">
-        <v>363</v>
-      </c>
-      <c r="G51" t="s">
-        <v>364</v>
-      </c>
-      <c r="H51" t="s">
-        <v>365</v>
-      </c>
-      <c r="I51" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>65</v>
-      </c>
-      <c r="B52" t="s">
-        <v>367</v>
-      </c>
-      <c r="C52" t="s">
-        <v>10</v>
-      </c>
-      <c r="D52" t="s">
-        <v>368</v>
-      </c>
-      <c r="E52" t="s">
-        <v>369</v>
-      </c>
-      <c r="F52" t="s">
-        <v>370</v>
-      </c>
-      <c r="G52" t="s">
-        <v>371</v>
-      </c>
-      <c r="H52" t="s">
-        <v>372</v>
-      </c>
-      <c r="I52" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>66</v>
-      </c>
-      <c r="B53" t="s">
-        <v>374</v>
-      </c>
-      <c r="C53" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" t="s">
-        <v>375</v>
-      </c>
-      <c r="E53" t="s">
-        <v>376</v>
-      </c>
-      <c r="F53" t="s">
-        <v>377</v>
-      </c>
-      <c r="G53" t="s">
-        <v>378</v>
-      </c>
-      <c r="H53" t="s">
-        <v>379</v>
-      </c>
-      <c r="I53" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>67</v>
-      </c>
-      <c r="B54" t="s">
-        <v>381</v>
-      </c>
-      <c r="C54" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" t="s">
-        <v>382</v>
-      </c>
-      <c r="E54" t="s">
-        <v>383</v>
-      </c>
-      <c r="F54" t="s">
-        <v>383</v>
-      </c>
-      <c r="G54" t="s">
-        <v>384</v>
-      </c>
-      <c r="H54" t="s">
-        <v>385</v>
-      </c>
-      <c r="I54" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>68</v>
-      </c>
-      <c r="B55" t="s">
-        <v>387</v>
-      </c>
-      <c r="C55" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" t="s">
-        <v>388</v>
-      </c>
-      <c r="E55" t="s">
-        <v>389</v>
-      </c>
-      <c r="F55" t="s">
-        <v>390</v>
-      </c>
-      <c r="G55" t="s">
-        <v>391</v>
-      </c>
-      <c r="H55" t="s">
-        <v>392</v>
-      </c>
-      <c r="I55" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>69</v>
-      </c>
-      <c r="B56" t="s">
-        <v>394</v>
-      </c>
-      <c r="C56" t="s">
-        <v>395</v>
-      </c>
-      <c r="D56" t="s">
-        <v>396</v>
-      </c>
-      <c r="E56" t="s">
-        <v>397</v>
-      </c>
-      <c r="F56" t="s">
-        <v>397</v>
-      </c>
-      <c r="G56" t="s">
-        <v>398</v>
-      </c>
-      <c r="H56" t="s">
-        <v>399</v>
-      </c>
-      <c r="I56" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>70</v>
-      </c>
-      <c r="B57" t="s">
-        <v>401</v>
-      </c>
-      <c r="C57" t="s">
-        <v>10</v>
-      </c>
-      <c r="D57" t="s">
-        <v>402</v>
-      </c>
-      <c r="E57" t="s">
-        <v>403</v>
-      </c>
-      <c r="F57" t="s">
-        <v>404</v>
-      </c>
-      <c r="G57" t="s">
-        <v>405</v>
-      </c>
-      <c r="H57" t="s">
-        <v>406</v>
-      </c>
-      <c r="I57" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A58">
-        <v>71</v>
-      </c>
-      <c r="B58" t="s">
-        <v>408</v>
-      </c>
-      <c r="C58" t="s">
-        <v>10</v>
-      </c>
-      <c r="D58" t="s">
-        <v>409</v>
-      </c>
-      <c r="E58" t="s">
-        <v>410</v>
-      </c>
-      <c r="F58" t="s">
-        <v>411</v>
-      </c>
-      <c r="G58" t="s">
-        <v>412</v>
-      </c>
-      <c r="H58" t="s">
-        <v>413</v>
-      </c>
-      <c r="I58" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A59">
-        <v>72</v>
-      </c>
-      <c r="B59" t="s">
-        <v>415</v>
-      </c>
-      <c r="C59" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" t="s">
-        <v>416</v>
-      </c>
-      <c r="E59" t="s">
-        <v>417</v>
-      </c>
-      <c r="F59" t="s">
-        <v>418</v>
-      </c>
-      <c r="G59" t="s">
-        <v>419</v>
-      </c>
-      <c r="H59" t="s">
-        <v>420</v>
-      </c>
-      <c r="I59" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>73</v>
-      </c>
-      <c r="B60" t="s">
-        <v>422</v>
-      </c>
-      <c r="C60" t="s">
-        <v>10</v>
-      </c>
-      <c r="D60" t="s">
-        <v>423</v>
-      </c>
-      <c r="E60" t="s">
-        <v>424</v>
-      </c>
-      <c r="F60" t="s">
-        <v>425</v>
-      </c>
-      <c r="G60" t="s">
-        <v>426</v>
-      </c>
-      <c r="H60" t="s">
-        <v>427</v>
-      </c>
-      <c r="I60" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>74</v>
-      </c>
-      <c r="B61" t="s">
-        <v>429</v>
-      </c>
-      <c r="C61" t="s">
-        <v>10</v>
-      </c>
-      <c r="D61" t="s">
-        <v>430</v>
-      </c>
-      <c r="E61" t="s">
-        <v>431</v>
-      </c>
-      <c r="F61" t="s">
-        <v>432</v>
-      </c>
-      <c r="G61" t="s">
-        <v>433</v>
-      </c>
-      <c r="H61" t="s">
-        <v>434</v>
-      </c>
-      <c r="I61" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>75</v>
-      </c>
-      <c r="B62" t="s">
-        <v>436</v>
-      </c>
-      <c r="C62" t="s">
-        <v>437</v>
-      </c>
-      <c r="D62" t="s">
-        <v>438</v>
-      </c>
-      <c r="E62" t="s">
-        <v>439</v>
-      </c>
-      <c r="F62" t="s">
-        <v>440</v>
-      </c>
-      <c r="G62" t="s">
-        <v>441</v>
-      </c>
-      <c r="H62" t="s">
-        <v>442</v>
-      </c>
-      <c r="I62" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>76</v>
-      </c>
-      <c r="B63" t="s">
-        <v>444</v>
-      </c>
-      <c r="C63" t="s">
-        <v>10</v>
-      </c>
-      <c r="D63" t="s">
-        <v>445</v>
-      </c>
-      <c r="E63" t="s">
-        <v>446</v>
-      </c>
-      <c r="F63" t="s">
-        <v>447</v>
-      </c>
-      <c r="G63" t="s">
-        <v>448</v>
-      </c>
-      <c r="H63" t="s">
-        <v>449</v>
-      </c>
-      <c r="I63" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>78</v>
-      </c>
-      <c r="B64" t="s">
-        <v>459</v>
-      </c>
-      <c r="C64" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" t="s">
-        <v>460</v>
-      </c>
-      <c r="E64" t="s">
-        <v>461</v>
-      </c>
-      <c r="F64" t="s">
-        <v>462</v>
-      </c>
-      <c r="G64" t="s">
-        <v>463</v>
-      </c>
-      <c r="H64" t="s">
-        <v>464</v>
-      </c>
-      <c r="I64" t="s">
+      <c r="B75" s="2" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>80</v>
-      </c>
-      <c r="B65" t="s">
-        <v>473</v>
-      </c>
-      <c r="C65" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" t="s">
-        <v>474</v>
-      </c>
-      <c r="E65" t="s">
-        <v>309</v>
-      </c>
-      <c r="F65" t="s">
-        <v>310</v>
-      </c>
-      <c r="G65" t="s">
-        <v>311</v>
-      </c>
-      <c r="H65" t="s">
-        <v>475</v>
-      </c>
-      <c r="I65" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>81</v>
-      </c>
-      <c r="B66" t="s">
-        <v>477</v>
-      </c>
-      <c r="C66" t="s">
-        <v>478</v>
-      </c>
-      <c r="D66" t="s">
-        <v>479</v>
-      </c>
-      <c r="E66" t="s">
-        <v>480</v>
-      </c>
-      <c r="F66" t="s">
-        <v>481</v>
-      </c>
-      <c r="G66" t="s">
-        <v>482</v>
-      </c>
-      <c r="H66" t="s">
-        <v>483</v>
-      </c>
-      <c r="I66" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>82</v>
-      </c>
-      <c r="B67" t="s">
-        <v>485</v>
-      </c>
-      <c r="C67" t="s">
-        <v>10</v>
-      </c>
-      <c r="D67" t="s">
-        <v>486</v>
-      </c>
-      <c r="E67" t="s">
-        <v>487</v>
-      </c>
-      <c r="F67" t="s">
-        <v>488</v>
-      </c>
-      <c r="G67" t="s">
-        <v>489</v>
-      </c>
-      <c r="H67" t="s">
-        <v>490</v>
-      </c>
-      <c r="I67" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A68">
-        <v>83</v>
-      </c>
-      <c r="B68" t="s">
-        <v>492</v>
-      </c>
-      <c r="C68" t="s">
-        <v>493</v>
-      </c>
-      <c r="D68" t="s">
-        <v>494</v>
-      </c>
-      <c r="E68" t="s">
-        <v>495</v>
-      </c>
-      <c r="F68" t="s">
-        <v>496</v>
-      </c>
-      <c r="G68" t="s">
-        <v>497</v>
-      </c>
-      <c r="H68" t="s">
-        <v>498</v>
-      </c>
-      <c r="I68" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>84</v>
-      </c>
-      <c r="B69" t="s">
-        <v>500</v>
-      </c>
-      <c r="C69" t="s">
-        <v>10</v>
-      </c>
-      <c r="D69" t="s">
-        <v>501</v>
-      </c>
-      <c r="E69" t="s">
-        <v>502</v>
-      </c>
-      <c r="F69" t="s">
-        <v>503</v>
-      </c>
-      <c r="G69" t="s">
-        <v>504</v>
-      </c>
-      <c r="H69" t="s">
-        <v>505</v>
-      </c>
-      <c r="I69" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>85</v>
-      </c>
-      <c r="B70" t="s">
-        <v>507</v>
-      </c>
-      <c r="C70" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" t="s">
-        <v>508</v>
-      </c>
-      <c r="E70" t="s">
-        <v>509</v>
-      </c>
-      <c r="F70" t="s">
-        <v>510</v>
-      </c>
-      <c r="G70" t="s">
-        <v>511</v>
-      </c>
-      <c r="H70" t="s">
-        <v>512</v>
-      </c>
-      <c r="I70" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>86</v>
-      </c>
-      <c r="B71" t="s">
-        <v>514</v>
-      </c>
-      <c r="C71" t="s">
-        <v>10</v>
-      </c>
-      <c r="D71" t="s">
-        <v>515</v>
-      </c>
-      <c r="E71" t="s">
-        <v>516</v>
-      </c>
-      <c r="F71" t="s">
-        <v>517</v>
-      </c>
-      <c r="G71" t="s">
-        <v>518</v>
-      </c>
-      <c r="H71" t="s">
-        <v>519</v>
-      </c>
-      <c r="I71" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>87</v>
-      </c>
-      <c r="B72" t="s">
-        <v>521</v>
-      </c>
-      <c r="C72" t="s">
-        <v>10</v>
-      </c>
-      <c r="D72" t="s">
-        <v>522</v>
-      </c>
-      <c r="E72" t="s">
-        <v>523</v>
-      </c>
-      <c r="F72" t="s">
-        <v>524</v>
-      </c>
-      <c r="G72" t="s">
-        <v>525</v>
-      </c>
-      <c r="H72" t="s">
-        <v>526</v>
-      </c>
-      <c r="I72" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>88</v>
-      </c>
-      <c r="B73" t="s">
-        <v>528</v>
-      </c>
-      <c r="C73" t="s">
-        <v>529</v>
-      </c>
-      <c r="D73" t="s">
-        <v>530</v>
-      </c>
-      <c r="E73" t="s">
-        <v>531</v>
-      </c>
-      <c r="F73" t="s">
-        <v>532</v>
-      </c>
-      <c r="G73" t="s">
-        <v>533</v>
-      </c>
-      <c r="H73" t="s">
-        <v>534</v>
-      </c>
-      <c r="I73" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>89</v>
-      </c>
-      <c r="B74" t="s">
-        <v>536</v>
-      </c>
-      <c r="C74" t="s">
-        <v>10</v>
-      </c>
-      <c r="D74" t="s">
-        <v>537</v>
-      </c>
-      <c r="E74" t="s">
-        <v>538</v>
-      </c>
-      <c r="F74" t="s">
-        <v>538</v>
-      </c>
-      <c r="G74" t="s">
-        <v>539</v>
-      </c>
-      <c r="H74" t="s">
-        <v>540</v>
-      </c>
-      <c r="I74" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>90</v>
-      </c>
-      <c r="B75" t="s">
-        <v>542</v>
-      </c>
-      <c r="C75" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" t="s">
-        <v>543</v>
-      </c>
-      <c r="E75" t="s">
-        <v>544</v>
+      <c r="C75" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>467</v>
       </c>
       <c r="F75" t="s">
-        <v>545</v>
+        <v>468</v>
       </c>
       <c r="G75" t="s">
-        <v>546</v>
-      </c>
-      <c r="H75" t="s">
-        <v>547</v>
-      </c>
-      <c r="I75" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:9" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="78" spans="1:9" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="79" spans="1:9" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="80" spans="1:9" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="88" ht="15.5" x14ac:dyDescent="0.35"/>
+        <v>470</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="93" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:I3 A49:I63 A48:I48 A35:I47 A31:I34 A30:I30 A17:I22 A8:I16 A7:I7 A6:I6 A4:I5 A65:I75 A64:I64 A23:I29" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B3 A49:B63 A48:B48 A35:B47 A31:B34 A30:B30 A17:B22 A8:B16 A7:B7 A6:B6 A4:B5 A65:B75 A64:B64 A23:B29 E1:F3 E49:F63 E48:F48 E35:F47 E31:F34 E30:F30 E17:F22 E8:F16 E7:F7 E6:F6 E4:F5 E65:F75 E64:F64 E23:F29 C1:C3 C49:C63 C48 C35:C47 C31:C34 C30 C17:C22 C8:C16 C7 C6 C4:C5 C65:C75 C64 C23:C29 G1:G3 G49:G63 G48 G35:G47 G31:G34 G30 G17:G22 G8:G16 G7 G6 G4:G5 G65:G75 G64 G23:G29" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J139"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="35.83203125" customWidth="1"/>
@@ -4869,7 +4193,7 @@
     <col min="10" max="10" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4880,1462 +4204,1462 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>549</v>
+        <v>471</v>
       </c>
       <c r="E1" t="s">
-        <v>550</v>
+        <v>472</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>551</v>
+        <v>473</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>552</v>
+        <v>474</v>
       </c>
       <c r="J1" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>557</v>
+        <v>479</v>
       </c>
       <c r="C2" t="s">
-        <v>558</v>
+        <v>480</v>
       </c>
       <c r="D2" t="s">
-        <v>559</v>
+        <v>481</v>
       </c>
       <c r="E2" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F2" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G2" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H2" t="s">
-        <v>560</v>
+        <v>482</v>
       </c>
       <c r="I2" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>562</v>
+        <v>484</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>563</v>
+        <v>485</v>
       </c>
       <c r="E3" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F3" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G3" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H3" t="s">
-        <v>564</v>
+        <v>486</v>
       </c>
       <c r="I3" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J3" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>566</v>
+        <v>488</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>567</v>
+        <v>489</v>
       </c>
       <c r="E4" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F4" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G4" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H4" t="s">
-        <v>568</v>
+        <v>490</v>
       </c>
       <c r="I4" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J4" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>570</v>
+        <v>492</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>571</v>
+        <v>493</v>
       </c>
       <c r="E5" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F5" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G5" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H5" t="s">
-        <v>572</v>
+        <v>494</v>
       </c>
       <c r="I5" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J5" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>574</v>
+        <v>496</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>575</v>
+        <v>497</v>
       </c>
       <c r="E6" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F6" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G6" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H6" t="s">
-        <v>576</v>
+        <v>498</v>
       </c>
       <c r="I6" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J6" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>578</v>
+        <v>500</v>
       </c>
       <c r="C7" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>734</v>
+        <v>656</v>
       </c>
       <c r="E7" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F7" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G7" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H7" t="s">
-        <v>580</v>
+        <v>502</v>
       </c>
       <c r="I7" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J7" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>582</v>
+        <v>504</v>
       </c>
       <c r="C8" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>733</v>
+        <v>655</v>
       </c>
       <c r="E8" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F8" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G8" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H8" t="s">
-        <v>583</v>
+        <v>505</v>
       </c>
       <c r="I8" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J8" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>585</v>
+        <v>507</v>
       </c>
       <c r="C9" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>732</v>
+        <v>654</v>
       </c>
       <c r="E9" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F9" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G9" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H9" t="s">
-        <v>586</v>
+        <v>508</v>
       </c>
       <c r="I9" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J9" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>588</v>
+        <v>510</v>
       </c>
       <c r="C10" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>731</v>
+        <v>653</v>
       </c>
       <c r="E10" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F10" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G10" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H10" t="s">
-        <v>589</v>
+        <v>511</v>
       </c>
       <c r="I10" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J10" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>591</v>
+        <v>513</v>
       </c>
       <c r="C11" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>730</v>
+        <v>652</v>
       </c>
       <c r="E11" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F11" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G11" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H11" t="s">
-        <v>592</v>
+        <v>514</v>
       </c>
       <c r="I11" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J11" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>594</v>
+        <v>516</v>
       </c>
       <c r="C12" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>729</v>
+        <v>651</v>
       </c>
       <c r="E12" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F12" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G12" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H12" t="s">
-        <v>595</v>
+        <v>517</v>
       </c>
       <c r="I12" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J12" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>597</v>
+        <v>519</v>
       </c>
       <c r="C13" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>728</v>
+        <v>650</v>
       </c>
       <c r="E13" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F13" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G13" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H13" t="s">
-        <v>598</v>
+        <v>520</v>
       </c>
       <c r="I13" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J13" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>600</v>
+        <v>522</v>
       </c>
       <c r="C14" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>727</v>
+        <v>649</v>
       </c>
       <c r="E14" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F14" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G14" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H14" t="s">
-        <v>601</v>
+        <v>523</v>
       </c>
       <c r="I14" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>603</v>
+        <v>525</v>
       </c>
       <c r="C15" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>726</v>
+        <v>648</v>
       </c>
       <c r="E15" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F15" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G15" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H15" t="s">
-        <v>604</v>
+        <v>526</v>
       </c>
       <c r="I15" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J15" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>72</v>
       </c>
       <c r="B16" t="s">
-        <v>606</v>
+        <v>528</v>
       </c>
       <c r="C16" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>725</v>
+        <v>647</v>
       </c>
       <c r="E16" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F16" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G16" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H16" t="s">
-        <v>607</v>
+        <v>529</v>
       </c>
       <c r="I16" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J16" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>73</v>
       </c>
       <c r="B17" t="s">
-        <v>609</v>
+        <v>531</v>
       </c>
       <c r="C17" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>724</v>
+        <v>646</v>
       </c>
       <c r="E17" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F17" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G17" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H17" t="s">
-        <v>610</v>
+        <v>532</v>
       </c>
       <c r="I17" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J17" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>612</v>
+        <v>534</v>
       </c>
       <c r="C18" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>723</v>
+        <v>645</v>
       </c>
       <c r="E18" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F18" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G18" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H18" t="s">
-        <v>613</v>
+        <v>535</v>
       </c>
       <c r="I18" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J18" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>615</v>
+        <v>537</v>
       </c>
       <c r="C19" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>722</v>
+        <v>644</v>
       </c>
       <c r="E19" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F19" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G19" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H19" t="s">
-        <v>616</v>
+        <v>538</v>
       </c>
       <c r="I19" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J19" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>618</v>
+        <v>540</v>
       </c>
       <c r="C20" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>721</v>
+        <v>643</v>
       </c>
       <c r="E20" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F20" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G20" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H20" t="s">
-        <v>619</v>
+        <v>541</v>
       </c>
       <c r="I20" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J20" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>621</v>
+        <v>543</v>
       </c>
       <c r="C21" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>720</v>
+        <v>642</v>
       </c>
       <c r="E21" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F21" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G21" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H21" t="s">
-        <v>622</v>
+        <v>544</v>
       </c>
       <c r="I21" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J21" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>624</v>
+        <v>546</v>
       </c>
       <c r="C22" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>719</v>
+        <v>641</v>
       </c>
       <c r="E22" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F22" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G22" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H22" t="s">
-        <v>625</v>
+        <v>547</v>
       </c>
       <c r="I22" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J22" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>627</v>
+        <v>549</v>
       </c>
       <c r="C23" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>718</v>
+        <v>640</v>
       </c>
       <c r="E23" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F23" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G23" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H23" t="s">
-        <v>628</v>
+        <v>550</v>
       </c>
       <c r="I23" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J23" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>630</v>
+        <v>552</v>
       </c>
       <c r="C24" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>717</v>
+        <v>639</v>
       </c>
       <c r="E24" t="s">
+        <v>476</v>
+      </c>
+      <c r="F24" t="s">
+        <v>477</v>
+      </c>
+      <c r="G24" t="s">
+        <v>477</v>
+      </c>
+      <c r="H24" t="s">
+        <v>553</v>
+      </c>
+      <c r="I24" t="s">
+        <v>478</v>
+      </c>
+      <c r="J24" t="s">
         <v>554</v>
       </c>
-      <c r="F24" t="s">
-        <v>555</v>
-      </c>
-      <c r="G24" t="s">
-        <v>555</v>
-      </c>
-      <c r="H24" t="s">
-        <v>631</v>
-      </c>
-      <c r="I24" t="s">
-        <v>556</v>
-      </c>
-      <c r="J24" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>94</v>
       </c>
       <c r="B25" t="s">
-        <v>633</v>
+        <v>555</v>
       </c>
       <c r="C25" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>716</v>
+        <v>638</v>
       </c>
       <c r="E25" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F25" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G25" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H25" t="s">
-        <v>634</v>
+        <v>556</v>
       </c>
       <c r="I25" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J25" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>96</v>
       </c>
       <c r="B26" t="s">
-        <v>636</v>
+        <v>558</v>
       </c>
       <c r="C26" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>715</v>
+        <v>637</v>
       </c>
       <c r="E26" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F26" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G26" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H26" t="s">
-        <v>637</v>
+        <v>559</v>
       </c>
       <c r="I26" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J26" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>639</v>
+        <v>561</v>
       </c>
       <c r="C27" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>714</v>
+        <v>636</v>
       </c>
       <c r="E27" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F27" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G27" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H27" t="s">
-        <v>640</v>
+        <v>562</v>
       </c>
       <c r="I27" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J27" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>99</v>
       </c>
       <c r="B28" t="s">
-        <v>642</v>
+        <v>564</v>
       </c>
       <c r="C28" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>713</v>
+        <v>635</v>
       </c>
       <c r="E28" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F28" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G28" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H28" t="s">
-        <v>643</v>
+        <v>565</v>
       </c>
       <c r="I28" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J28" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>645</v>
+        <v>567</v>
       </c>
       <c r="C29" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>712</v>
+        <v>634</v>
       </c>
       <c r="E29" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F29" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G29" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H29" t="s">
-        <v>646</v>
+        <v>568</v>
       </c>
       <c r="I29" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J29" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>104</v>
       </c>
       <c r="B30" t="s">
-        <v>648</v>
+        <v>570</v>
       </c>
       <c r="C30" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>711</v>
+        <v>633</v>
       </c>
       <c r="E30" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F30" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G30" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H30" t="s">
-        <v>649</v>
+        <v>571</v>
       </c>
       <c r="I30" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J30" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>105</v>
       </c>
       <c r="B31" t="s">
-        <v>651</v>
+        <v>573</v>
       </c>
       <c r="C31" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>710</v>
+        <v>632</v>
       </c>
       <c r="E31" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F31" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G31" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H31" t="s">
-        <v>652</v>
+        <v>574</v>
       </c>
       <c r="I31" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J31" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>108</v>
       </c>
       <c r="B32" t="s">
-        <v>654</v>
+        <v>576</v>
       </c>
       <c r="C32" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>709</v>
+        <v>631</v>
       </c>
       <c r="E32" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F32" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G32" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H32" t="s">
-        <v>655</v>
+        <v>577</v>
       </c>
       <c r="I32" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J32" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>109</v>
       </c>
       <c r="B33" t="s">
-        <v>657</v>
+        <v>579</v>
       </c>
       <c r="C33" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>708</v>
+        <v>630</v>
       </c>
       <c r="E33" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F33" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G33" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H33" t="s">
-        <v>658</v>
+        <v>580</v>
       </c>
       <c r="I33" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J33" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>660</v>
+        <v>582</v>
       </c>
       <c r="C34" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>707</v>
+        <v>629</v>
       </c>
       <c r="E34" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F34" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G34" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H34" t="s">
-        <v>661</v>
+        <v>583</v>
       </c>
       <c r="I34" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J34" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>111</v>
       </c>
       <c r="B35" t="s">
-        <v>663</v>
+        <v>585</v>
       </c>
       <c r="C35" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>706</v>
+        <v>628</v>
       </c>
       <c r="E35" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F35" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G35" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H35" t="s">
-        <v>664</v>
+        <v>586</v>
       </c>
       <c r="I35" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J35" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>112</v>
       </c>
       <c r="B36" t="s">
-        <v>666</v>
+        <v>588</v>
       </c>
       <c r="C36" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>705</v>
+        <v>627</v>
       </c>
       <c r="E36" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F36" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G36" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H36" t="s">
-        <v>667</v>
+        <v>589</v>
       </c>
       <c r="I36" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J36" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>669</v>
+        <v>591</v>
       </c>
       <c r="C37" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>704</v>
+        <v>626</v>
       </c>
       <c r="E37" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F37" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G37" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H37" t="s">
-        <v>670</v>
+        <v>592</v>
       </c>
       <c r="I37" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J37" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>119</v>
       </c>
       <c r="B38" t="s">
-        <v>672</v>
+        <v>594</v>
       </c>
       <c r="C38" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>703</v>
+        <v>625</v>
       </c>
       <c r="E38" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F38" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G38" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H38" t="s">
-        <v>673</v>
+        <v>595</v>
       </c>
       <c r="I38" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J38" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>124</v>
       </c>
       <c r="B39" t="s">
-        <v>675</v>
+        <v>597</v>
       </c>
       <c r="C39" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>702</v>
+        <v>624</v>
       </c>
       <c r="E39" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F39" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G39" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H39" t="s">
-        <v>676</v>
+        <v>598</v>
       </c>
       <c r="I39" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J39" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>125</v>
       </c>
       <c r="B40" t="s">
-        <v>678</v>
+        <v>600</v>
       </c>
       <c r="C40" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>701</v>
+        <v>623</v>
       </c>
       <c r="E40" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F40" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G40" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H40" t="s">
-        <v>679</v>
+        <v>601</v>
       </c>
       <c r="I40" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J40" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>128</v>
       </c>
       <c r="B41" t="s">
-        <v>681</v>
+        <v>603</v>
       </c>
       <c r="C41" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>700</v>
+        <v>622</v>
       </c>
       <c r="E41" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F41" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G41" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H41" t="s">
-        <v>682</v>
+        <v>604</v>
       </c>
       <c r="I41" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J41" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>129</v>
       </c>
       <c r="B42" t="s">
-        <v>684</v>
+        <v>606</v>
       </c>
       <c r="C42" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>699</v>
+        <v>621</v>
       </c>
       <c r="E42" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F42" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G42" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H42" t="s">
-        <v>685</v>
+        <v>607</v>
       </c>
       <c r="I42" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J42" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>131</v>
       </c>
       <c r="B43" t="s">
-        <v>687</v>
+        <v>609</v>
       </c>
       <c r="C43" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>698</v>
+        <v>620</v>
       </c>
       <c r="E43" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F43" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G43" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H43" t="s">
-        <v>688</v>
+        <v>610</v>
       </c>
       <c r="I43" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J43" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>132</v>
       </c>
       <c r="B44" t="s">
-        <v>690</v>
+        <v>612</v>
       </c>
       <c r="C44" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>697</v>
+        <v>619</v>
       </c>
       <c r="E44" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F44" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G44" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H44" t="s">
-        <v>691</v>
+        <v>613</v>
       </c>
       <c r="I44" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J44" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>135</v>
       </c>
       <c r="B45" t="s">
-        <v>693</v>
+        <v>615</v>
       </c>
       <c r="C45" t="s">
-        <v>579</v>
+        <v>501</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>696</v>
+        <v>618</v>
       </c>
       <c r="E45" t="s">
-        <v>554</v>
+        <v>476</v>
       </c>
       <c r="F45" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="G45" t="s">
-        <v>555</v>
+        <v>477</v>
       </c>
       <c r="H45" t="s">
-        <v>694</v>
+        <v>616</v>
       </c>
       <c r="I45" t="s">
-        <v>556</v>
+        <v>478</v>
       </c>
       <c r="J45" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="C46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="E46" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="F46" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="G46" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="H46" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="I46" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
@@ -6343,123 +5667,59 @@
         <v>77</v>
       </c>
       <c r="B47" t="s">
-        <v>451</v>
+        <v>386</v>
       </c>
       <c r="C47" t="s">
-        <v>452</v>
+        <v>387</v>
       </c>
       <c r="D47" t="s">
-        <v>453</v>
+        <v>388</v>
       </c>
       <c r="E47" t="s">
-        <v>454</v>
+        <v>389</v>
       </c>
       <c r="F47" t="s">
-        <v>455</v>
+        <v>390</v>
       </c>
       <c r="G47" t="s">
-        <v>456</v>
+        <v>391</v>
       </c>
       <c r="H47" t="s">
-        <v>457</v>
+        <v>392</v>
       </c>
       <c r="I47" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>79</v>
       </c>
       <c r="B48" t="s">
-        <v>466</v>
+        <v>400</v>
       </c>
       <c r="C48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>467</v>
+        <v>401</v>
       </c>
       <c r="E48" t="s">
-        <v>468</v>
+        <v>402</v>
       </c>
       <c r="F48" t="s">
-        <v>469</v>
+        <v>403</v>
       </c>
       <c r="G48" t="s">
-        <v>470</v>
+        <v>404</v>
       </c>
       <c r="H48" t="s">
-        <v>471</v>
+        <v>405</v>
       </c>
       <c r="I48" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="50" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="51" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="52" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="53" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="57" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="62" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="64" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="86" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="89" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="90" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="94" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="95" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="96" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="97" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="98" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="99" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="100" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="101" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="102" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="103" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="105" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="106" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="110" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="111" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="112" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="113" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="114" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="115" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="116" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="117" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="118" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="119" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="121" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="122" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="126" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="127" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="128" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="130" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="131" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="132" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="133" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="134" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="135" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="136" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="137" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="138" ht="15.5" x14ac:dyDescent="0.35"/>
-    <row r="139" ht="15.5" x14ac:dyDescent="0.35"/>
+        <v>406</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
